--- a/output/nabos_01_02avg.xlsx
+++ b/output/nabos_01_02avg.xlsx
@@ -559,61 +559,61 @@
         <v>-0.616</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6145</v>
+        <v>-0.6144</v>
       </c>
       <c r="G2" t="n">
-        <v>22.127985</v>
+        <v>22.127833</v>
       </c>
       <c r="H2" t="n">
-        <v>22.125384</v>
+        <v>22.122381</v>
       </c>
       <c r="I2" t="n">
-        <v>26.4986</v>
+        <v>26.4983</v>
       </c>
       <c r="J2" t="n">
-        <v>26.4939</v>
+        <v>26.4898</v>
       </c>
       <c r="K2" t="n">
-        <v>370.524</v>
+        <v>370.536</v>
       </c>
       <c r="L2" t="n">
-        <v>363.359</v>
+        <v>363.296</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0847</v>
+        <v>0.0822</v>
       </c>
       <c r="N2" t="n">
-        <v>4.58</v>
+        <v>4.5795</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1035</v>
+        <v>0.1036</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1035</v>
+        <v>0.1036</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0941</v>
+        <v>0.0946</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0284</v>
+        <v>0.0283</v>
       </c>
       <c r="S2" t="n">
-        <v>2261</v>
+        <v>2271</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5693</v>
+        <v>1.5763</v>
       </c>
       <c r="U2" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="V2" t="n">
         <v>2.5984</v>
       </c>
       <c r="W2" t="n">
-        <v>2.2639</v>
+        <v>2.2635</v>
       </c>
       <c r="X2" t="n">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -636,7 +636,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4.948</v>
+        <v>4.947</v>
       </c>
       <c r="B3" t="n">
         <v>73.77036</v>
@@ -648,64 +648,64 @@
         <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.615</v>
+        <v>-0.6149</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6149</v>
+        <v>-0.6147</v>
       </c>
       <c r="G3" t="n">
-        <v>22.115252</v>
+        <v>22.114349</v>
       </c>
       <c r="H3" t="n">
-        <v>22.114311</v>
+        <v>22.113789</v>
       </c>
       <c r="I3" t="n">
-        <v>26.4806</v>
+        <v>26.4793</v>
       </c>
       <c r="J3" t="n">
-        <v>26.4792</v>
+        <v>26.4784</v>
       </c>
       <c r="K3" t="n">
-        <v>370.613</v>
+        <v>370.596</v>
       </c>
       <c r="L3" t="n">
-        <v>362.405</v>
+        <v>362.39</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1013</v>
+        <v>0.0993</v>
       </c>
       <c r="N3" t="n">
         <v>4.5779</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1034</v>
+        <v>0.1035</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1034</v>
+        <v>0.1035</v>
       </c>
       <c r="Q3" t="n">
         <v>0.0959</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0291</v>
+        <v>0.029</v>
       </c>
       <c r="S3" t="n">
-        <v>2415</v>
+        <v>2422</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6765</v>
+        <v>1.6811</v>
       </c>
       <c r="U3" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="V3" t="n">
-        <v>2.5984</v>
+        <v>2.5983</v>
       </c>
       <c r="W3" t="n">
-        <v>2.2588</v>
+        <v>2.2587</v>
       </c>
       <c r="X3" t="n">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -728,7 +728,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5.938</v>
+        <v>5.94</v>
       </c>
       <c r="B4" t="n">
         <v>73.77036</v>
@@ -740,64 +740,64 @@
         <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6179</v>
+        <v>-0.6186</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6172</v>
+        <v>-0.6174</v>
       </c>
       <c r="G4" t="n">
-        <v>22.120578</v>
+        <v>22.122334</v>
       </c>
       <c r="H4" t="n">
-        <v>22.119313</v>
+        <v>22.1194</v>
       </c>
       <c r="I4" t="n">
-        <v>26.4896</v>
+        <v>26.4926</v>
       </c>
       <c r="J4" t="n">
-        <v>26.4873</v>
+        <v>26.4877</v>
       </c>
       <c r="K4" t="n">
-        <v>370.922</v>
+        <v>370.891</v>
       </c>
       <c r="L4" t="n">
-        <v>363.402</v>
+        <v>363.225</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1061</v>
+        <v>0.1073</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5818</v>
+        <v>4.5812</v>
       </c>
       <c r="O4" t="n">
-        <v>0.103</v>
+        <v>0.1031</v>
       </c>
       <c r="P4" t="n">
-        <v>0.103</v>
+        <v>0.1031</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0925</v>
+        <v>0.093</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0292</v>
+        <v>0.0293</v>
       </c>
       <c r="S4" t="n">
-        <v>2542</v>
+        <v>2547</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7643</v>
+        <v>1.7678</v>
       </c>
       <c r="U4" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="V4" t="n">
-        <v>2.5998</v>
+        <v>2.5996</v>
       </c>
       <c r="W4" t="n">
-        <v>2.2634</v>
+        <v>2.2625</v>
       </c>
       <c r="X4" t="n">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -832,55 +832,55 @@
         <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6238</v>
+        <v>-0.624</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.624</v>
+        <v>-0.6243</v>
       </c>
       <c r="G5" t="n">
-        <v>22.138212</v>
+        <v>22.139068</v>
       </c>
       <c r="H5" t="n">
-        <v>22.138849</v>
+        <v>22.139783</v>
       </c>
       <c r="I5" t="n">
-        <v>26.5173</v>
+        <v>26.5189</v>
       </c>
       <c r="J5" t="n">
-        <v>26.5184</v>
+        <v>26.5201</v>
       </c>
       <c r="K5" t="n">
-        <v>370.557</v>
+        <v>370.569</v>
       </c>
       <c r="L5" t="n">
-        <v>362.754</v>
+        <v>362.751</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1241</v>
+        <v>0.1204</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5796</v>
+        <v>4.5799</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1034</v>
+        <v>0.1035</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1034</v>
+        <v>0.1035</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0945</v>
+        <v>0.0942</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03</v>
+        <v>0.0298</v>
       </c>
       <c r="S5" t="n">
-        <v>2665</v>
+        <v>2668</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8501</v>
+        <v>1.8522</v>
       </c>
       <c r="U5" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="V5" t="n">
         <v>2.5976</v>
@@ -889,7 +889,7 @@
         <v>2.2601</v>
       </c>
       <c r="X5" t="n">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -924,64 +924,64 @@
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6406</v>
+        <v>-0.6414</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6412</v>
+        <v>-0.642</v>
       </c>
       <c r="G6" t="n">
-        <v>22.206503</v>
+        <v>22.206863</v>
       </c>
       <c r="H6" t="n">
-        <v>22.203357</v>
+        <v>22.203166</v>
       </c>
       <c r="I6" t="n">
-        <v>26.6211</v>
+        <v>26.6229</v>
       </c>
       <c r="J6" t="n">
-        <v>26.6176</v>
+        <v>26.6186</v>
       </c>
       <c r="K6" t="n">
-        <v>370.393</v>
+        <v>370.391</v>
       </c>
       <c r="L6" t="n">
-        <v>362.658</v>
+        <v>362.575</v>
       </c>
       <c r="M6" t="n">
-        <v>0.116</v>
+        <v>0.115</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5765</v>
+        <v>4.5759</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1028</v>
+        <v>0.1027</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1028</v>
+        <v>0.1027</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0972</v>
+        <v>0.0977</v>
       </c>
       <c r="R6" t="n">
         <v>0.0296</v>
       </c>
       <c r="S6" t="n">
-        <v>2751</v>
+        <v>2755</v>
       </c>
       <c r="T6" t="n">
-        <v>1.9094</v>
+        <v>1.9122</v>
       </c>
       <c r="U6" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="V6" t="n">
         <v>2.597</v>
       </c>
       <c r="W6" t="n">
-        <v>2.2599</v>
+        <v>2.2594</v>
       </c>
       <c r="X6" t="n">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1004,7 +1004,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>8.907</v>
+        <v>8.905</v>
       </c>
       <c r="B7" t="n">
         <v>73.77036</v>
@@ -1016,64 +1016,64 @@
         <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6413</v>
+        <v>-0.6415</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6445</v>
+        <v>-0.6462</v>
       </c>
       <c r="G7" t="n">
-        <v>22.225395</v>
+        <v>22.22521</v>
       </c>
       <c r="H7" t="n">
-        <v>22.231412</v>
+        <v>22.235865</v>
       </c>
       <c r="I7" t="n">
-        <v>26.646</v>
+        <v>26.6463</v>
       </c>
       <c r="J7" t="n">
-        <v>26.6567</v>
+        <v>26.6646</v>
       </c>
       <c r="K7" t="n">
-        <v>370.809</v>
+        <v>370.807</v>
       </c>
       <c r="L7" t="n">
-        <v>363.012</v>
+        <v>363.261</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1056</v>
+        <v>0.1057</v>
       </c>
       <c r="N7" t="n">
-        <v>4.5791</v>
+        <v>4.5782</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1021</v>
+        <v>0.1022</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1021</v>
+        <v>0.1022</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0949</v>
+        <v>0.0957</v>
       </c>
       <c r="R7" t="n">
         <v>0.0292</v>
       </c>
       <c r="S7" t="n">
-        <v>2831</v>
+        <v>2834</v>
       </c>
       <c r="T7" t="n">
-        <v>1.9652</v>
+        <v>1.9675</v>
       </c>
       <c r="U7" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="V7" t="n">
         <v>2.5994</v>
       </c>
       <c r="W7" t="n">
-        <v>2.2617</v>
+        <v>2.2629</v>
       </c>
       <c r="X7" t="n">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1096,7 +1096,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>9.896</v>
+        <v>9.897</v>
       </c>
       <c r="B8" t="n">
         <v>73.77038</v>
@@ -1108,64 +1108,64 @@
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6353</v>
+        <v>-0.6348</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6363</v>
+        <v>-0.636</v>
       </c>
       <c r="G8" t="n">
-        <v>22.218859</v>
+        <v>22.21796</v>
       </c>
       <c r="H8" t="n">
-        <v>22.218619</v>
+        <v>22.218075</v>
       </c>
       <c r="I8" t="n">
-        <v>26.6317</v>
+        <v>26.6301</v>
       </c>
       <c r="J8" t="n">
-        <v>26.6322</v>
+        <v>26.6313</v>
       </c>
       <c r="K8" t="n">
-        <v>370.873</v>
+        <v>370.852</v>
       </c>
       <c r="L8" t="n">
-        <v>362.853</v>
+        <v>362.928</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1218</v>
+        <v>0.123</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5812</v>
+        <v>4.5809</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1032</v>
+        <v>0.1034</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1032</v>
+        <v>0.1034</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0931</v>
+        <v>0.0934</v>
       </c>
       <c r="R8" t="n">
         <v>0.0299</v>
       </c>
       <c r="S8" t="n">
-        <v>2891</v>
+        <v>2893</v>
       </c>
       <c r="T8" t="n">
-        <v>2.0071</v>
+        <v>2.0081</v>
       </c>
       <c r="U8" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="V8" t="n">
-        <v>2.5996</v>
+        <v>2.5995</v>
       </c>
       <c r="W8" t="n">
-        <v>2.2608</v>
+        <v>2.2612</v>
       </c>
       <c r="X8" t="n">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1188,76 +1188,76 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>10.886</v>
+        <v>10.884</v>
       </c>
       <c r="B9" t="n">
         <v>73.77038</v>
       </c>
       <c r="C9" t="n">
-        <v>167.70402</v>
+        <v>167.70401</v>
       </c>
       <c r="D9" t="n">
         <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6459</v>
+        <v>-0.6457</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.652</v>
+        <v>-0.6529</v>
       </c>
       <c r="G9" t="n">
-        <v>22.231855</v>
+        <v>22.231516</v>
       </c>
       <c r="H9" t="n">
-        <v>22.238745</v>
+        <v>22.239462</v>
       </c>
       <c r="I9" t="n">
-        <v>26.6575</v>
+        <v>26.6573</v>
       </c>
       <c r="J9" t="n">
-        <v>26.672</v>
+        <v>26.6743</v>
       </c>
       <c r="K9" t="n">
-        <v>371.006</v>
+        <v>370.997</v>
       </c>
       <c r="L9" t="n">
-        <v>363.383</v>
+        <v>363.358</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1222</v>
+        <v>0.1198</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5825</v>
+        <v>4.5822</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1041</v>
+        <v>0.1042</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1041</v>
+        <v>0.1042</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0919</v>
+        <v>0.0921</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0299</v>
+        <v>0.0298</v>
       </c>
       <c r="S9" t="n">
-        <v>2948</v>
+        <v>2949</v>
       </c>
       <c r="T9" t="n">
-        <v>2.0464</v>
+        <v>2.0475</v>
       </c>
       <c r="U9" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="V9" t="n">
-        <v>2.5999</v>
+        <v>2.5998</v>
       </c>
       <c r="W9" t="n">
-        <v>2.2628</v>
+        <v>2.2627</v>
       </c>
       <c r="X9" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1280,76 +1280,76 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>11.876</v>
+        <v>11.877</v>
       </c>
       <c r="B10" t="n">
         <v>73.77038</v>
       </c>
       <c r="C10" t="n">
-        <v>167.70402</v>
+        <v>167.70403</v>
       </c>
       <c r="D10" t="n">
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6472</v>
+        <v>-0.6469</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6555</v>
+        <v>-0.6549</v>
       </c>
       <c r="G10" t="n">
-        <v>22.235089</v>
+        <v>22.234725</v>
       </c>
       <c r="H10" t="n">
-        <v>22.246568</v>
+        <v>22.245492</v>
       </c>
       <c r="I10" t="n">
-        <v>26.6624</v>
+        <v>26.662</v>
       </c>
       <c r="J10" t="n">
-        <v>26.6848</v>
+        <v>26.6833</v>
       </c>
       <c r="K10" t="n">
-        <v>370.937</v>
+        <v>370.955</v>
       </c>
       <c r="L10" t="n">
-        <v>363.149</v>
+        <v>363.107</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1335</v>
+        <v>0.135</v>
       </c>
       <c r="N10" t="n">
         <v>4.5792</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1047</v>
+        <v>0.1046</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1047</v>
+        <v>0.1046</v>
       </c>
       <c r="Q10" t="n">
         <v>0.0948</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0303</v>
+        <v>0.0304</v>
       </c>
       <c r="S10" t="n">
-        <v>2996</v>
+        <v>2997</v>
       </c>
       <c r="T10" t="n">
-        <v>2.0795</v>
+        <v>2.0806</v>
       </c>
       <c r="U10" t="n">
         <v>0.01</v>
       </c>
       <c r="V10" t="n">
-        <v>2.5992</v>
+        <v>2.5993</v>
       </c>
       <c r="W10" t="n">
-        <v>2.2615</v>
+        <v>2.2613</v>
       </c>
       <c r="X10" t="n">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1384,64 +1384,64 @@
         <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6365</v>
+        <v>-0.637</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6445</v>
+        <v>-0.6464</v>
       </c>
       <c r="G11" t="n">
-        <v>22.218103</v>
+        <v>22.218225</v>
       </c>
       <c r="H11" t="n">
-        <v>22.233544</v>
+        <v>22.236003</v>
       </c>
       <c r="I11" t="n">
-        <v>26.6301</v>
+        <v>26.6308</v>
       </c>
       <c r="J11" t="n">
-        <v>26.6575</v>
+        <v>26.6625</v>
       </c>
       <c r="K11" t="n">
-        <v>371.034</v>
+        <v>370.999</v>
       </c>
       <c r="L11" t="n">
-        <v>362.302</v>
+        <v>362.297</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1213</v>
+        <v>0.1216</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5813</v>
+        <v>4.5815</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1028</v>
+        <v>0.1029</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1028</v>
+        <v>0.1029</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.093</v>
+        <v>0.0928</v>
       </c>
       <c r="R11" t="n">
         <v>0.0298</v>
       </c>
       <c r="S11" t="n">
-        <v>3049</v>
+        <v>3050</v>
       </c>
       <c r="T11" t="n">
-        <v>2.1163</v>
+        <v>2.1171</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="V11" t="n">
-        <v>2.5996</v>
+        <v>2.5994</v>
       </c>
       <c r="W11" t="n">
-        <v>2.2574</v>
+        <v>2.2573</v>
       </c>
       <c r="X11" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1476,64 +1476,64 @@
         <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6644</v>
+        <v>-0.6653</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6632</v>
+        <v>-0.6627</v>
       </c>
       <c r="G12" t="n">
-        <v>22.272359</v>
+        <v>22.274725</v>
       </c>
       <c r="H12" t="n">
-        <v>22.266204</v>
+        <v>22.265109</v>
       </c>
       <c r="I12" t="n">
-        <v>26.7255</v>
+        <v>26.7302</v>
       </c>
       <c r="J12" t="n">
-        <v>26.7163</v>
+        <v>26.7151</v>
       </c>
       <c r="K12" t="n">
-        <v>370.885</v>
+        <v>370.877</v>
       </c>
       <c r="L12" t="n">
-        <v>363.302</v>
+        <v>363.481</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1209</v>
+        <v>0.121</v>
       </c>
       <c r="N12" t="n">
-        <v>4.5805</v>
+        <v>4.5807</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1018</v>
+        <v>0.102</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1018</v>
+        <v>0.102</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0937</v>
+        <v>0.0935</v>
       </c>
       <c r="R12" t="n">
         <v>0.0298</v>
       </c>
       <c r="S12" t="n">
-        <v>3098</v>
+        <v>3099</v>
       </c>
       <c r="T12" t="n">
-        <v>2.1505</v>
+        <v>2.1513</v>
       </c>
       <c r="U12" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="V12" t="n">
         <v>2.5983</v>
       </c>
       <c r="W12" t="n">
-        <v>2.2618</v>
+        <v>2.2626</v>
       </c>
       <c r="X12" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -1568,64 +1568,64 @@
         <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6878</v>
+        <v>-0.6874</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6874</v>
+        <v>-0.6885</v>
       </c>
       <c r="G13" t="n">
-        <v>22.32828</v>
+        <v>22.326279</v>
       </c>
       <c r="H13" t="n">
-        <v>22.326655</v>
+        <v>22.329656</v>
       </c>
       <c r="I13" t="n">
-        <v>26.8192</v>
+        <v>26.8175</v>
       </c>
       <c r="J13" t="n">
-        <v>26.8167</v>
+        <v>26.8228</v>
       </c>
       <c r="K13" t="n">
-        <v>370.479</v>
+        <v>370.452</v>
       </c>
       <c r="L13" t="n">
-        <v>363.933</v>
+        <v>363.758</v>
       </c>
       <c r="M13" t="n">
-        <v>0.126</v>
+        <v>0.121</v>
       </c>
       <c r="N13" t="n">
-        <v>4.579</v>
+        <v>4.5788</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1031</v>
+        <v>0.1032</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1031</v>
+        <v>0.1032</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.095</v>
+        <v>0.0951</v>
       </c>
       <c r="R13" t="n">
-        <v>0.03</v>
+        <v>0.0298</v>
       </c>
       <c r="S13" t="n">
-        <v>3149</v>
+        <v>3151</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1863</v>
+        <v>2.1872</v>
       </c>
       <c r="U13" t="n">
         <v>0.29</v>
       </c>
       <c r="V13" t="n">
-        <v>2.5958</v>
+        <v>2.5956</v>
       </c>
       <c r="W13" t="n">
-        <v>2.2647</v>
+        <v>2.2639</v>
       </c>
       <c r="X13" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -1660,64 +1660,64 @@
         <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.7802</v>
+        <v>-0.8015</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7503</v>
+        <v>-0.7671</v>
       </c>
       <c r="G14" t="n">
-        <v>22.521056</v>
+        <v>22.560149</v>
       </c>
       <c r="H14" t="n">
-        <v>22.461085</v>
+        <v>22.492908</v>
       </c>
       <c r="I14" t="n">
-        <v>27.1566</v>
+        <v>27.2324</v>
       </c>
       <c r="J14" t="n">
-        <v>27.0499</v>
+        <v>27.1107</v>
       </c>
       <c r="K14" t="n">
-        <v>370.448</v>
+        <v>370.433</v>
       </c>
       <c r="L14" t="n">
-        <v>361.95</v>
+        <v>361.933</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1087</v>
+        <v>0.1107</v>
       </c>
       <c r="N14" t="n">
-        <v>4.5779</v>
+        <v>4.5774</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1044</v>
+        <v>0.1043</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1044</v>
+        <v>0.1043</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.096</v>
+        <v>0.0964</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0293</v>
+        <v>0.0294</v>
       </c>
       <c r="S14" t="n">
-        <v>3201</v>
+        <v>3202</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2222</v>
+        <v>2.2231</v>
       </c>
       <c r="U14" t="n">
-        <v>0.27</v>
+        <v>0.21</v>
       </c>
       <c r="V14" t="n">
-        <v>2.595</v>
+        <v>2.5948</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2548</v>
+        <v>2.2546</v>
       </c>
       <c r="X14" t="n">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -1740,7 +1740,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16.824</v>
+        <v>16.823</v>
       </c>
       <c r="B15" t="n">
         <v>73.77038</v>
@@ -1752,64 +1752,64 @@
         <v>17</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.1157</v>
+        <v>-1.1136</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1087</v>
+        <v>-1.1081</v>
       </c>
       <c r="G15" t="n">
-        <v>23.119507</v>
+        <v>23.104593</v>
       </c>
       <c r="H15" t="n">
-        <v>23.106097</v>
+        <v>23.093395</v>
       </c>
       <c r="I15" t="n">
-        <v>28.2586</v>
+        <v>28.2495</v>
       </c>
       <c r="J15" t="n">
-        <v>28.2341</v>
+        <v>28.2294</v>
       </c>
       <c r="K15" t="n">
-        <v>369.238</v>
+        <v>369.158</v>
       </c>
       <c r="L15" t="n">
-        <v>362.137</v>
+        <v>361.903</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2252</v>
+        <v>0.2185</v>
       </c>
       <c r="N15" t="n">
-        <v>4.5796</v>
+        <v>4.5786</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1095</v>
+        <v>0.1097</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1095</v>
+        <v>0.1097</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0945</v>
+        <v>0.0953</v>
       </c>
       <c r="R15" t="n">
-        <v>0.034</v>
+        <v>0.0337</v>
       </c>
       <c r="S15" t="n">
-        <v>3255</v>
+        <v>3256</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2597</v>
+        <v>2.2604</v>
       </c>
       <c r="U15" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="V15" t="n">
-        <v>2.5847</v>
+        <v>2.5842</v>
       </c>
       <c r="W15" t="n">
-        <v>2.2527</v>
+        <v>2.2516</v>
       </c>
       <c r="X15" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -1832,7 +1832,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>17.813</v>
+        <v>17.814</v>
       </c>
       <c r="B16" t="n">
         <v>73.77038</v>
@@ -1844,34 +1844,34 @@
         <v>18</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.1439</v>
+        <v>-1.1444</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.138</v>
+        <v>-1.1377</v>
       </c>
       <c r="G16" t="n">
-        <v>23.163709</v>
+        <v>23.157512</v>
       </c>
       <c r="H16" t="n">
-        <v>23.156622</v>
+        <v>23.149886</v>
       </c>
       <c r="I16" t="n">
-        <v>28.3444</v>
+        <v>28.347</v>
       </c>
       <c r="J16" t="n">
-        <v>28.3294</v>
+        <v>28.3304</v>
       </c>
       <c r="K16" t="n">
-        <v>365.809</v>
+        <v>365.689</v>
       </c>
       <c r="L16" t="n">
-        <v>360.031</v>
+        <v>359.967</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2282</v>
+        <v>0.2288</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4266</v>
+        <v>4.4355</v>
       </c>
       <c r="O16" t="n">
         <v>0.1114</v>
@@ -1880,28 +1880,28 @@
         <v>0.1114</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.2332</v>
+        <v>0.2251</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0341</v>
+        <v>0.0342</v>
       </c>
       <c r="S16" t="n">
-        <v>3303</v>
+        <v>3304</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2928</v>
+        <v>2.2936</v>
       </c>
       <c r="U16" t="n">
         <v>0.18</v>
       </c>
       <c r="V16" t="n">
-        <v>2.5646</v>
+        <v>2.5639</v>
       </c>
       <c r="W16" t="n">
-        <v>2.2422</v>
+        <v>2.2419</v>
       </c>
       <c r="X16" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -1924,7 +1924,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>18.803</v>
+        <v>18.802</v>
       </c>
       <c r="B17" t="n">
         <v>73.77038</v>
@@ -1936,34 +1936,34 @@
         <v>19</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1805</v>
+        <v>-1.1817</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1833</v>
+        <v>-1.1844</v>
       </c>
       <c r="G17" t="n">
-        <v>23.215887</v>
+        <v>23.211242</v>
       </c>
       <c r="H17" t="n">
-        <v>23.212528</v>
+        <v>23.207294</v>
       </c>
       <c r="I17" t="n">
-        <v>28.4486</v>
+        <v>28.4522</v>
       </c>
       <c r="J17" t="n">
-        <v>28.4467</v>
+        <v>28.4498</v>
       </c>
       <c r="K17" t="n">
-        <v>361.109</v>
+        <v>360.942</v>
       </c>
       <c r="L17" t="n">
-        <v>356.835</v>
+        <v>356.86</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3113</v>
+        <v>0.3146</v>
       </c>
       <c r="N17" t="n">
-        <v>4.5713</v>
+        <v>4.5761</v>
       </c>
       <c r="O17" t="n">
         <v>0.1116</v>
@@ -1972,28 +1972,28 @@
         <v>0.1116</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.1018</v>
+        <v>0.0975</v>
       </c>
       <c r="R17" t="n">
-        <v>0.0375</v>
+        <v>0.0376</v>
       </c>
       <c r="S17" t="n">
-        <v>3354</v>
+        <v>3355</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3284</v>
+        <v>2.3294</v>
       </c>
       <c r="U17" t="n">
         <v>0.28</v>
       </c>
       <c r="V17" t="n">
-        <v>2.5371</v>
+        <v>2.5361</v>
       </c>
       <c r="W17" t="n">
-        <v>2.2259</v>
+        <v>2.226</v>
       </c>
       <c r="X17" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -2016,7 +2016,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>19.792</v>
+        <v>19.793</v>
       </c>
       <c r="B18" t="n">
         <v>73.7704</v>
@@ -2028,34 +2028,34 @@
         <v>20</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1938</v>
+        <v>-1.1943</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1909</v>
+        <v>-1.1914</v>
       </c>
       <c r="G18" t="n">
-        <v>23.246579</v>
+        <v>23.242535</v>
       </c>
       <c r="H18" t="n">
-        <v>23.22933</v>
+        <v>23.226103</v>
       </c>
       <c r="I18" t="n">
-        <v>28.5018</v>
+        <v>28.5038</v>
       </c>
       <c r="J18" t="n">
-        <v>28.4759</v>
+        <v>28.4791</v>
       </c>
       <c r="K18" t="n">
-        <v>357.656</v>
+        <v>357.567</v>
       </c>
       <c r="L18" t="n">
-        <v>352.147</v>
+        <v>352.107</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2655</v>
+        <v>0.2593</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5889</v>
+        <v>4.5894</v>
       </c>
       <c r="O18" t="n">
         <v>0.1125</v>
@@ -2064,28 +2064,28 @@
         <v>0.1125</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.0863</v>
+        <v>0.0859</v>
       </c>
       <c r="R18" t="n">
-        <v>0.0356</v>
+        <v>0.0354</v>
       </c>
       <c r="S18" t="n">
-        <v>3404</v>
+        <v>3405</v>
       </c>
       <c r="T18" t="n">
-        <v>2.3629</v>
+        <v>2.364</v>
       </c>
       <c r="U18" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="V18" t="n">
-        <v>2.5173</v>
+        <v>2.5168</v>
       </c>
       <c r="W18" t="n">
-        <v>2.2032</v>
+        <v>2.203</v>
       </c>
       <c r="X18" t="n">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -2108,13 +2108,13 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>20.782</v>
+        <v>20.781</v>
       </c>
       <c r="B19" t="n">
         <v>73.7704</v>
       </c>
       <c r="C19" t="n">
-        <v>167.70417</v>
+        <v>167.70418</v>
       </c>
       <c r="D19" t="n">
         <v>21</v>
@@ -2123,31 +2123,31 @@
         <v>-1.2078</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2095</v>
+        <v>-1.2096</v>
       </c>
       <c r="G19" t="n">
-        <v>23.258526</v>
+        <v>23.254123</v>
       </c>
       <c r="H19" t="n">
-        <v>23.258822</v>
+        <v>23.253701</v>
       </c>
       <c r="I19" t="n">
-        <v>28.5307</v>
+        <v>28.5302</v>
       </c>
       <c r="J19" t="n">
-        <v>28.5327</v>
+        <v>28.5315</v>
       </c>
       <c r="K19" t="n">
-        <v>355.123</v>
+        <v>355.069</v>
       </c>
       <c r="L19" t="n">
-        <v>350.717</v>
+        <v>350.853</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2731</v>
+        <v>0.2745</v>
       </c>
       <c r="N19" t="n">
-        <v>4.5943</v>
+        <v>4.594</v>
       </c>
       <c r="O19" t="n">
         <v>0.1134</v>
@@ -2156,28 +2156,28 @@
         <v>0.1134</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.0817</v>
+        <v>0.0818</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0359</v>
+        <v>0.036</v>
       </c>
       <c r="S19" t="n">
-        <v>3458</v>
+        <v>3460</v>
       </c>
       <c r="T19" t="n">
-        <v>2.4009</v>
+        <v>2.4018</v>
       </c>
       <c r="U19" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="V19" t="n">
-        <v>2.5023</v>
+        <v>2.502</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1959</v>
+        <v>2.1966</v>
       </c>
       <c r="X19" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -2212,34 +2212,34 @@
         <v>22</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.255</v>
+        <v>-1.2536</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.256</v>
+        <v>-1.2558</v>
       </c>
       <c r="G20" t="n">
-        <v>23.314643</v>
+        <v>23.309012</v>
       </c>
       <c r="H20" t="n">
-        <v>23.314326</v>
+        <v>23.31001</v>
       </c>
       <c r="I20" t="n">
+        <v>28.6473</v>
+      </c>
+      <c r="J20" t="n">
         <v>28.6508</v>
       </c>
-      <c r="J20" t="n">
-        <v>28.6513</v>
-      </c>
       <c r="K20" t="n">
-        <v>354.126</v>
+        <v>354.06</v>
       </c>
       <c r="L20" t="n">
-        <v>346.048</v>
+        <v>346.174</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2832</v>
+        <v>0.2827</v>
       </c>
       <c r="N20" t="n">
-        <v>4.5953</v>
+        <v>4.5948</v>
       </c>
       <c r="O20" t="n">
         <v>0.1123</v>
@@ -2248,28 +2248,28 @@
         <v>0.1123</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.0808</v>
+        <v>0.0812</v>
       </c>
       <c r="R20" t="n">
         <v>0.0363</v>
       </c>
       <c r="S20" t="n">
-        <v>3509</v>
+        <v>3510</v>
       </c>
       <c r="T20" t="n">
-        <v>2.4359</v>
+        <v>2.4366</v>
       </c>
       <c r="U20" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V20" t="n">
-        <v>2.4954</v>
+        <v>2.495</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1726</v>
+        <v>2.1732</v>
       </c>
       <c r="X20" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -2304,64 +2304,64 @@
         <v>23</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.26</v>
+        <v>-1.2611</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2558</v>
+        <v>-1.2567</v>
       </c>
       <c r="G21" t="n">
-        <v>23.316702</v>
+        <v>23.314771</v>
       </c>
       <c r="H21" t="n">
-        <v>23.309791</v>
+        <v>23.307787</v>
       </c>
       <c r="I21" t="n">
-        <v>28.6578</v>
+        <v>28.6605</v>
       </c>
       <c r="J21" t="n">
-        <v>28.6445</v>
+        <v>28.6468</v>
       </c>
       <c r="K21" t="n">
-        <v>352.096</v>
+        <v>352.043</v>
       </c>
       <c r="L21" t="n">
-        <v>345.502</v>
+        <v>345.464</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2465</v>
+        <v>0.2457</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5957</v>
+        <v>4.5961</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1129</v>
+        <v>0.113</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1129</v>
+        <v>0.113</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.0804</v>
+        <v>0.0801</v>
       </c>
       <c r="R21" t="n">
-        <v>0.0349</v>
+        <v>0.0348</v>
       </c>
       <c r="S21" t="n">
-        <v>3558</v>
+        <v>3559</v>
       </c>
       <c r="T21" t="n">
-        <v>2.4703</v>
+        <v>2.4711</v>
       </c>
       <c r="U21" t="n">
         <v>0.43</v>
       </c>
       <c r="V21" t="n">
-        <v>2.4835</v>
+        <v>2.4831</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1697</v>
+        <v>2.1695</v>
       </c>
       <c r="X21" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -2396,40 +2396,40 @@
         <v>24</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2942</v>
+        <v>-1.2952</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2868</v>
+        <v>-1.2875</v>
       </c>
       <c r="G22" t="n">
-        <v>23.365376</v>
+        <v>23.363422</v>
       </c>
       <c r="H22" t="n">
-        <v>23.352731</v>
+        <v>23.350655</v>
       </c>
       <c r="I22" t="n">
-        <v>28.7557</v>
+        <v>28.7582</v>
       </c>
       <c r="J22" t="n">
-        <v>28.7315</v>
+        <v>28.7334</v>
       </c>
       <c r="K22" t="n">
-        <v>349.127</v>
+        <v>349.047</v>
       </c>
       <c r="L22" t="n">
-        <v>343.645</v>
+        <v>343.656</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2444</v>
+        <v>0.2461</v>
       </c>
       <c r="N22" t="n">
         <v>4.5973</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1163</v>
+        <v>0.1165</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1163</v>
+        <v>0.1165</v>
       </c>
       <c r="Q22" t="n">
         <v>0.079</v>
@@ -2438,22 +2438,22 @@
         <v>0.0348</v>
       </c>
       <c r="S22" t="n">
-        <v>3610</v>
+        <v>3611</v>
       </c>
       <c r="T22" t="n">
-        <v>2.5061</v>
+        <v>2.5069</v>
       </c>
       <c r="U22" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="V22" t="n">
-        <v>2.4659</v>
+        <v>2.4654</v>
       </c>
       <c r="W22" t="n">
         <v>2.1602</v>
       </c>
       <c r="X22" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -2488,34 +2488,34 @@
         <v>25</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3221</v>
+        <v>-1.3216</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3275</v>
+        <v>-1.3285</v>
       </c>
       <c r="G23" t="n">
-        <v>23.397967</v>
+        <v>23.394316</v>
       </c>
       <c r="H23" t="n">
-        <v>23.401461</v>
+        <v>23.399512</v>
       </c>
       <c r="I23" t="n">
-        <v>28.8259</v>
+        <v>28.8244</v>
       </c>
       <c r="J23" t="n">
-        <v>28.8359</v>
+        <v>28.8384</v>
       </c>
       <c r="K23" t="n">
-        <v>346.603</v>
+        <v>346.549</v>
       </c>
       <c r="L23" t="n">
-        <v>340.872</v>
+        <v>340.836</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2202</v>
+        <v>0.2221</v>
       </c>
       <c r="N23" t="n">
-        <v>4.5897</v>
+        <v>4.5898</v>
       </c>
       <c r="O23" t="n">
         <v>0.1156</v>
@@ -2527,25 +2527,25 @@
         <v>0.0856</v>
       </c>
       <c r="R23" t="n">
-        <v>0.0338</v>
+        <v>0.0339</v>
       </c>
       <c r="S23" t="n">
-        <v>3663</v>
+        <v>3664</v>
       </c>
       <c r="T23" t="n">
-        <v>2.543</v>
+        <v>2.5437</v>
       </c>
       <c r="U23" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="V23" t="n">
-        <v>2.4508</v>
+        <v>2.4504</v>
       </c>
       <c r="W23" t="n">
-        <v>2.146</v>
+        <v>2.1458</v>
       </c>
       <c r="X23" t="n">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -2580,34 +2580,34 @@
         <v>26</v>
       </c>
       <c r="E24" t="n">
+        <v>-1.3375</v>
+      </c>
+      <c r="F24" t="n">
         <v>-1.3372</v>
       </c>
-      <c r="F24" t="n">
-        <v>-1.3371</v>
-      </c>
       <c r="G24" t="n">
-        <v>23.408906</v>
+        <v>23.406634</v>
       </c>
       <c r="H24" t="n">
-        <v>23.407494</v>
+        <v>23.405138</v>
       </c>
       <c r="I24" t="n">
-        <v>28.8548</v>
+        <v>28.8553</v>
       </c>
       <c r="J24" t="n">
-        <v>28.8527</v>
+        <v>28.853</v>
       </c>
       <c r="K24" t="n">
-        <v>344.126</v>
+        <v>344.079</v>
       </c>
       <c r="L24" t="n">
-        <v>338.709</v>
+        <v>338.561</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2279</v>
+        <v>0.2286</v>
       </c>
       <c r="N24" t="n">
-        <v>4.6031</v>
+        <v>4.6038</v>
       </c>
       <c r="O24" t="n">
         <v>0.1154</v>
@@ -2616,28 +2616,28 @@
         <v>0.1154</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.074</v>
+        <v>0.0734</v>
       </c>
       <c r="R24" t="n">
-        <v>0.0341</v>
+        <v>0.0342</v>
       </c>
       <c r="S24" t="n">
-        <v>3715</v>
+        <v>3716</v>
       </c>
       <c r="T24" t="n">
-        <v>2.579</v>
+        <v>2.58</v>
       </c>
       <c r="U24" t="n">
-        <v>0.08</v>
+        <v>0.07</v>
       </c>
       <c r="V24" t="n">
-        <v>2.436</v>
+        <v>2.4358</v>
       </c>
       <c r="W24" t="n">
-        <v>2.1352</v>
+        <v>2.1345</v>
       </c>
       <c r="X24" t="n">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
         <v>73.7704</v>
       </c>
       <c r="C25" t="n">
-        <v>167.7043</v>
+        <v>167.70431</v>
       </c>
       <c r="D25" t="n">
         <v>27</v>
@@ -2675,31 +2675,31 @@
         <v>-1.3435</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.3431</v>
+        <v>-1.343</v>
       </c>
       <c r="G25" t="n">
-        <v>23.416277</v>
+        <v>23.414385</v>
       </c>
       <c r="H25" t="n">
-        <v>23.414529</v>
+        <v>23.412572</v>
       </c>
       <c r="I25" t="n">
-        <v>28.8702</v>
+        <v>28.8703</v>
       </c>
       <c r="J25" t="n">
-        <v>28.8675</v>
+        <v>28.8674</v>
       </c>
       <c r="K25" t="n">
-        <v>340.887</v>
+        <v>340.818</v>
       </c>
       <c r="L25" t="n">
-        <v>335.135</v>
+        <v>335.079</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2137</v>
+        <v>0.2139</v>
       </c>
       <c r="N25" t="n">
-        <v>4.5978</v>
+        <v>4.5985</v>
       </c>
       <c r="O25" t="n">
         <v>0.1151</v>
@@ -2708,28 +2708,28 @@
         <v>0.1151</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.0786</v>
+        <v>0.078</v>
       </c>
       <c r="R25" t="n">
         <v>0.0336</v>
       </c>
       <c r="S25" t="n">
-        <v>3767</v>
+        <v>3768</v>
       </c>
       <c r="T25" t="n">
-        <v>2.6154</v>
+        <v>2.616</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>2.4174</v>
+        <v>2.417</v>
       </c>
       <c r="W25" t="n">
-        <v>2.1178</v>
+        <v>2.1176</v>
       </c>
       <c r="X25" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>27.709</v>
+        <v>27.71</v>
       </c>
       <c r="B26" t="n">
         <v>73.7704</v>
@@ -2764,34 +2764,34 @@
         <v>28</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.3531</v>
+        <v>-1.3536</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.3529</v>
+        <v>-1.3533</v>
       </c>
       <c r="G26" t="n">
-        <v>23.429873</v>
+        <v>23.42884</v>
       </c>
       <c r="H26" t="n">
-        <v>23.428241</v>
+        <v>23.427242</v>
       </c>
       <c r="I26" t="n">
-        <v>28.8974</v>
+        <v>28.8988</v>
       </c>
       <c r="J26" t="n">
-        <v>28.895</v>
+        <v>28.8963</v>
       </c>
       <c r="K26" t="n">
-        <v>338.022</v>
+        <v>337.916</v>
       </c>
       <c r="L26" t="n">
-        <v>333.073</v>
+        <v>333.172</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2247</v>
+        <v>0.2235</v>
       </c>
       <c r="N26" t="n">
-        <v>4.6063</v>
+        <v>4.6068</v>
       </c>
       <c r="O26" t="n">
         <v>0.1164</v>
@@ -2800,28 +2800,28 @@
         <v>0.1164</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.0712</v>
+        <v>0.0708</v>
       </c>
       <c r="R26" t="n">
         <v>0.034</v>
       </c>
       <c r="S26" t="n">
-        <v>3814</v>
+        <v>3816</v>
       </c>
       <c r="T26" t="n">
-        <v>2.6481</v>
+        <v>2.6494</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>2.4008</v>
+        <v>2.4002</v>
       </c>
       <c r="W26" t="n">
-        <v>2.1076</v>
+        <v>2.1081</v>
       </c>
       <c r="X26" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -2856,34 +2856,34 @@
         <v>29</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.3708</v>
+        <v>-1.3714</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.3673</v>
+        <v>-1.368</v>
       </c>
       <c r="G27" t="n">
-        <v>23.446665</v>
+        <v>23.445638</v>
       </c>
       <c r="H27" t="n">
-        <v>23.442543</v>
+        <v>23.441806</v>
       </c>
       <c r="I27" t="n">
-        <v>28.9367</v>
+        <v>28.938</v>
       </c>
       <c r="J27" t="n">
-        <v>28.9277</v>
+        <v>28.9295</v>
       </c>
       <c r="K27" t="n">
-        <v>336.398</v>
+        <v>336.321</v>
       </c>
       <c r="L27" t="n">
-        <v>330.144</v>
+        <v>330.067</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1974</v>
+        <v>0.1961</v>
       </c>
       <c r="N27" t="n">
-        <v>4.6128</v>
+        <v>4.6129</v>
       </c>
       <c r="O27" t="n">
         <v>0.1159</v>
@@ -2892,28 +2892,28 @@
         <v>0.1159</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.0655</v>
+        <v>0.0654</v>
       </c>
       <c r="R27" t="n">
         <v>0.0329</v>
       </c>
       <c r="S27" t="n">
-        <v>3870</v>
+        <v>3872</v>
       </c>
       <c r="T27" t="n">
-        <v>2.6866</v>
+        <v>2.688</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>0.07</v>
       </c>
       <c r="V27" t="n">
-        <v>2.3909</v>
+        <v>2.3905</v>
       </c>
       <c r="W27" t="n">
-        <v>2.0932</v>
+        <v>2.0928</v>
       </c>
       <c r="X27" t="n">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>29.688</v>
+        <v>29.687</v>
       </c>
       <c r="B28" t="n">
         <v>73.7704</v>
@@ -2948,64 +2948,64 @@
         <v>30</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.3842</v>
+        <v>-1.3843</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.3838</v>
+        <v>-1.3839</v>
       </c>
       <c r="G28" t="n">
-        <v>23.464751</v>
+        <v>23.463599</v>
       </c>
       <c r="H28" t="n">
-        <v>23.463354</v>
+        <v>23.462233</v>
       </c>
       <c r="I28" t="n">
-        <v>28.9736</v>
+        <v>28.9741</v>
       </c>
       <c r="J28" t="n">
-        <v>28.9713</v>
+        <v>28.9719</v>
       </c>
       <c r="K28" t="n">
-        <v>333.985</v>
+        <v>333.906</v>
       </c>
       <c r="L28" t="n">
-        <v>329.018</v>
+        <v>329.005</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1644</v>
+        <v>0.1622</v>
       </c>
       <c r="N28" t="n">
-        <v>4.6151</v>
+        <v>4.615</v>
       </c>
       <c r="O28" t="n">
-        <v>0.1149</v>
+        <v>0.115</v>
       </c>
       <c r="P28" t="n">
-        <v>0.1149</v>
+        <v>0.115</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.0636</v>
+        <v>0.0637</v>
       </c>
       <c r="R28" t="n">
-        <v>0.0315</v>
+        <v>0.0314</v>
       </c>
       <c r="S28" t="n">
-        <v>3924</v>
+        <v>3925</v>
       </c>
       <c r="T28" t="n">
-        <v>2.7241</v>
+        <v>2.725</v>
       </c>
       <c r="U28" t="n">
         <v>0.01</v>
       </c>
       <c r="V28" t="n">
-        <v>2.3768</v>
+        <v>2.3764</v>
       </c>
       <c r="W28" t="n">
-        <v>2.0874</v>
+        <v>2.0873</v>
       </c>
       <c r="X28" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>30.678</v>
+        <v>30.679</v>
       </c>
       <c r="B29" t="n">
         <v>73.7704</v>
@@ -3040,64 +3040,64 @@
         <v>31</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.3916</v>
+        <v>-1.3918</v>
       </c>
       <c r="F29" t="n">
         <v>-1.3904</v>
       </c>
       <c r="G29" t="n">
-        <v>23.480745</v>
+        <v>23.480311</v>
       </c>
       <c r="H29" t="n">
-        <v>23.47836</v>
+        <v>23.477743</v>
       </c>
       <c r="I29" t="n">
-        <v>29.0019</v>
+        <v>29.0031</v>
       </c>
       <c r="J29" t="n">
-        <v>28.9975</v>
+        <v>28.9983</v>
       </c>
       <c r="K29" t="n">
-        <v>330.761</v>
+        <v>330.622</v>
       </c>
       <c r="L29" t="n">
-        <v>326.431</v>
+        <v>326.424</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1256</v>
+        <v>0.124</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6142</v>
+        <v>4.6147</v>
       </c>
       <c r="O29" t="n">
-        <v>0.1155</v>
+        <v>0.1154</v>
       </c>
       <c r="P29" t="n">
-        <v>0.1155</v>
+        <v>0.1154</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.0643</v>
+        <v>0.0639</v>
       </c>
       <c r="R29" t="n">
-        <v>0.03</v>
+        <v>0.0299</v>
       </c>
       <c r="S29" t="n">
-        <v>3972</v>
+        <v>3974</v>
       </c>
       <c r="T29" t="n">
-        <v>2.7577</v>
+        <v>2.7591</v>
       </c>
       <c r="U29" t="n">
-        <v>0.4</v>
+        <v>0.52</v>
       </c>
       <c r="V29" t="n">
-        <v>2.3584</v>
+        <v>2.3576</v>
       </c>
       <c r="W29" t="n">
         <v>2.0748</v>
       </c>
       <c r="X29" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -3120,7 +3120,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>31.667</v>
+        <v>31.668</v>
       </c>
       <c r="B30" t="n">
         <v>73.7704</v>
@@ -3132,34 +3132,34 @@
         <v>32</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.3974</v>
+        <v>-1.3975</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.3956</v>
+        <v>-1.3958</v>
       </c>
       <c r="G30" t="n">
-        <v>23.499648</v>
+        <v>23.498984</v>
       </c>
       <c r="H30" t="n">
-        <v>23.496229</v>
+        <v>23.495616</v>
       </c>
       <c r="I30" t="n">
-        <v>29.0325</v>
+        <v>29.0331</v>
       </c>
       <c r="J30" t="n">
-        <v>29.0261</v>
+        <v>29.0268</v>
       </c>
       <c r="K30" t="n">
-        <v>326.257</v>
+        <v>326.068</v>
       </c>
       <c r="L30" t="n">
-        <v>322.358</v>
+        <v>322.087</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1097</v>
+        <v>0.1039</v>
       </c>
       <c r="N30" t="n">
-        <v>4.6187</v>
+        <v>4.6183</v>
       </c>
       <c r="O30" t="n">
         <v>0.1168</v>
@@ -3168,28 +3168,28 @@
         <v>0.1168</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.0604</v>
+        <v>0.0607</v>
       </c>
       <c r="R30" t="n">
-        <v>0.0294</v>
+        <v>0.0291</v>
       </c>
       <c r="S30" t="n">
-        <v>4036</v>
+        <v>4040</v>
       </c>
       <c r="T30" t="n">
-        <v>2.8022</v>
+        <v>2.8046</v>
       </c>
       <c r="U30" t="n">
-        <v>0.51</v>
+        <v>0.44</v>
       </c>
       <c r="V30" t="n">
-        <v>2.3329</v>
+        <v>2.3318</v>
       </c>
       <c r="W30" t="n">
-        <v>2.0553</v>
+        <v>2.054</v>
       </c>
       <c r="X30" t="n">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -3224,34 +3224,34 @@
         <v>33</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.4024</v>
+        <v>-1.4029</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.4017</v>
+        <v>-1.402</v>
       </c>
       <c r="G31" t="n">
-        <v>23.518349</v>
+        <v>23.520051</v>
       </c>
       <c r="H31" t="n">
-        <v>23.515615</v>
+        <v>23.516795</v>
       </c>
       <c r="I31" t="n">
-        <v>29.0621</v>
+        <v>29.0659</v>
       </c>
       <c r="J31" t="n">
-        <v>29.0577</v>
+        <v>29.0605</v>
       </c>
       <c r="K31" t="n">
-        <v>322.147</v>
+        <v>322.213</v>
       </c>
       <c r="L31" t="n">
-        <v>317.658</v>
+        <v>317.47</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0636</v>
+        <v>0.0663</v>
       </c>
       <c r="N31" t="n">
-        <v>4.6205</v>
+        <v>4.6206</v>
       </c>
       <c r="O31" t="n">
         <v>0.1166</v>
@@ -3260,28 +3260,28 @@
         <v>0.1166</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.0589</v>
+        <v>0.0588</v>
       </c>
       <c r="R31" t="n">
-        <v>0.0276</v>
+        <v>0.0277</v>
       </c>
       <c r="S31" t="n">
-        <v>4126</v>
+        <v>4130</v>
       </c>
       <c r="T31" t="n">
-        <v>2.8647</v>
+        <v>2.8677</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="V31" t="n">
-        <v>2.3096</v>
+        <v>2.31</v>
       </c>
       <c r="W31" t="n">
-        <v>2.0328</v>
+        <v>2.0319</v>
       </c>
       <c r="X31" t="n">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
@@ -3316,34 +3316,34 @@
         <v>34</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.4128</v>
+        <v>-1.4133</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.4113</v>
+        <v>-1.4118</v>
       </c>
       <c r="G32" t="n">
-        <v>23.563372</v>
+        <v>23.565421</v>
       </c>
       <c r="H32" t="n">
-        <v>23.557335</v>
+        <v>23.558992</v>
       </c>
       <c r="I32" t="n">
-        <v>29.1327</v>
+        <v>29.1368</v>
       </c>
       <c r="J32" t="n">
-        <v>29.1231</v>
+        <v>29.1266</v>
       </c>
       <c r="K32" t="n">
-        <v>322.526</v>
+        <v>322.428</v>
       </c>
       <c r="L32" t="n">
-        <v>316.393</v>
+        <v>316.486</v>
       </c>
       <c r="M32" t="n">
-        <v>0.133</v>
+        <v>0.1436</v>
       </c>
       <c r="N32" t="n">
-        <v>4.6202</v>
+        <v>4.6198</v>
       </c>
       <c r="O32" t="n">
         <v>0.1166</v>
@@ -3352,28 +3352,28 @@
         <v>0.1166</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.0591</v>
+        <v>0.0595</v>
       </c>
       <c r="R32" t="n">
-        <v>0.0303</v>
+        <v>0.0307</v>
       </c>
       <c r="S32" t="n">
-        <v>4224</v>
+        <v>4229</v>
       </c>
       <c r="T32" t="n">
-        <v>2.933</v>
+        <v>2.9364</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="V32" t="n">
-        <v>2.3119</v>
+        <v>2.3114</v>
       </c>
       <c r="W32" t="n">
-        <v>2.0269</v>
+        <v>2.0274</v>
       </c>
       <c r="X32" t="n">
-        <v>17</v>
+        <v>108</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>34.636</v>
+        <v>34.635</v>
       </c>
       <c r="B33" t="n">
         <v>73.77042</v>
@@ -3408,64 +3408,64 @@
         <v>35</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.4206</v>
+        <v>-1.4209</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.4194</v>
+        <v>-1.4197</v>
       </c>
       <c r="G33" t="n">
-        <v>23.605918</v>
+        <v>23.606368</v>
       </c>
       <c r="H33" t="n">
-        <v>23.602116</v>
+        <v>23.602828</v>
       </c>
       <c r="I33" t="n">
-        <v>29.1974</v>
+        <v>29.1989</v>
       </c>
       <c r="J33" t="n">
-        <v>29.191</v>
+        <v>29.1929</v>
       </c>
       <c r="K33" t="n">
-        <v>315.626</v>
+        <v>315.163</v>
       </c>
       <c r="L33" t="n">
-        <v>312.286</v>
+        <v>312.063</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1955</v>
+        <v>0.2011</v>
       </c>
       <c r="N33" t="n">
-        <v>4.6059</v>
+        <v>4.6047</v>
       </c>
       <c r="O33" t="n">
-        <v>0.1189</v>
+        <v>0.1186</v>
       </c>
       <c r="P33" t="n">
-        <v>0.1189</v>
+        <v>0.1186</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.0715</v>
+        <v>0.0726</v>
       </c>
       <c r="R33" t="n">
-        <v>0.0328</v>
+        <v>0.0331</v>
       </c>
       <c r="S33" t="n">
-        <v>4331</v>
+        <v>4336</v>
       </c>
       <c r="T33" t="n">
-        <v>3.0072</v>
+        <v>3.0104</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>2.2732</v>
+        <v>2.2706</v>
       </c>
       <c r="W33" t="n">
-        <v>2.0076</v>
+        <v>2.0065</v>
       </c>
       <c r="X33" t="n">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -3503,61 +3503,61 @@
         <v>-1.4243</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.4232</v>
+        <v>-1.4233</v>
       </c>
       <c r="G34" t="n">
-        <v>23.625274</v>
+        <v>23.626253</v>
       </c>
       <c r="H34" t="n">
-        <v>23.62126</v>
+        <v>23.622267</v>
       </c>
       <c r="I34" t="n">
-        <v>29.2268</v>
+        <v>29.2284</v>
       </c>
       <c r="J34" t="n">
-        <v>29.2202</v>
+        <v>29.2221</v>
       </c>
       <c r="K34" t="n">
-        <v>300.96</v>
+        <v>300.048</v>
       </c>
       <c r="L34" t="n">
-        <v>300.401</v>
+        <v>299.466</v>
       </c>
       <c r="M34" t="n">
-        <v>0.2036</v>
+        <v>0.1997</v>
       </c>
       <c r="N34" t="n">
-        <v>4.5621</v>
+        <v>4.5591</v>
       </c>
       <c r="O34" t="n">
-        <v>0.1183</v>
+        <v>0.1182</v>
       </c>
       <c r="P34" t="n">
-        <v>0.1183</v>
+        <v>0.1182</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.1098</v>
+        <v>0.1125</v>
       </c>
       <c r="R34" t="n">
-        <v>0.0332</v>
+        <v>0.033</v>
       </c>
       <c r="S34" t="n">
-        <v>4445</v>
+        <v>4453</v>
       </c>
       <c r="T34" t="n">
-        <v>3.0862</v>
+        <v>3.0914</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="V34" t="n">
-        <v>2.1905</v>
+        <v>2.1853</v>
       </c>
       <c r="W34" t="n">
-        <v>1.9509</v>
+        <v>1.9464</v>
       </c>
       <c r="X34" t="n">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
@@ -3580,10 +3580,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>36.615</v>
+        <v>36.616</v>
       </c>
       <c r="B35" t="n">
-        <v>73.77045</v>
+        <v>73.77044</v>
       </c>
       <c r="C35" t="n">
         <v>167.70457</v>
@@ -3592,64 +3592,64 @@
         <v>37</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.421</v>
+        <v>-1.4205</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.4206</v>
+        <v>-1.4199</v>
       </c>
       <c r="G35" t="n">
-        <v>23.6901</v>
+        <v>23.690697</v>
       </c>
       <c r="H35" t="n">
-        <v>23.683523</v>
+        <v>23.68863</v>
       </c>
       <c r="I35" t="n">
-        <v>29.3108</v>
+        <v>29.3112</v>
       </c>
       <c r="J35" t="n">
-        <v>29.3015</v>
+        <v>29.3077</v>
       </c>
       <c r="K35" t="n">
-        <v>296.659</v>
+        <v>297.71</v>
       </c>
       <c r="L35" t="n">
-        <v>290.551</v>
+        <v>291.184</v>
       </c>
       <c r="M35" t="n">
-        <v>0.289</v>
+        <v>0.2891</v>
       </c>
       <c r="N35" t="n">
-        <v>4.4914</v>
+        <v>4.487</v>
       </c>
       <c r="O35" t="n">
-        <v>0.1183</v>
+        <v>0.1185</v>
       </c>
       <c r="P35" t="n">
-        <v>0.1183</v>
+        <v>0.1185</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.1725</v>
+        <v>0.1764</v>
       </c>
       <c r="R35" t="n">
         <v>0.0366</v>
       </c>
       <c r="S35" t="n">
-        <v>4678</v>
+        <v>4688</v>
       </c>
       <c r="T35" t="n">
-        <v>3.2477</v>
+        <v>3.255</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="V35" t="n">
-        <v>2.1673</v>
+        <v>2.1733</v>
       </c>
       <c r="W35" t="n">
-        <v>1.9047</v>
+        <v>1.9078</v>
       </c>
       <c r="X35" t="n">
-        <v>15</v>
+        <v>203</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
